--- a/output/full_scan/batch_seq0_2026-10-07.xlsx
+++ b/output/full_scan/batch_seq0_2026-10-07.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>946.602670879616</v>
+        <v>1101.602670879615</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>8.890000000000001</v>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.63049937699096</v>
+        <v>61.63049946346785</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>18.43799825780701</v>
+        <v>18.43799828825638</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.777600364887542</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0248114986836246</v>
+        <v>0.0248114986769486</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>930.3331557743504</v>
+        <v>1100.33315577435</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>126</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.05690777761212</v>
+        <v>61.05690777986359</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>25.3739948435797</v>
+        <v>25.37399482021501</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>3.133315577435047</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>1.328978289331384</v>
+        <v>1.328978289487168</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8926</v>
+        <v>8213</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>924.0886911289476</v>
+        <v>1094</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>60.3</v>
+        <v>37.7</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>58.98116860485109</v>
+        <v>76.26374714608977</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>13.70952889144838</v>
+        <v>25.98855328016623</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.516968016283242</v>
+        <v>9.39680734435391</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,11 +676,11 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.2112637251083644</v>
+        <v>0.3465120217456718</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>889.2627340638705</v>
+        <v>1059.26273406387</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>145</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>58.16510858120843</v>
+        <v>58.16510855045529</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>13.52574999226787</v>
+        <v>13.52574996232198</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>3.47253850183653</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.572325022176287</v>
+        <v>1.572325022220801</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>817.087650732877</v>
+        <v>1042.087650732877</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>20.9</v>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>63.59894059419164</v>
+        <v>63.59894055187059</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>18.24220502107331</v>
+        <v>18.24220504657312</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>2.700836018230738</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1380568008842244</v>
+        <v>0.1380568009064811</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8086</v>
+        <v>8926</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>816.3963440468985</v>
+        <v>1034.088691128948</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>140</v>
+        <v>60.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>76.04401523031771</v>
+        <v>58.98116866741561</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>22.91579593610674</v>
+        <v>13.70952891623057</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.239634404689856</v>
+        <v>1.516968016283242</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>3.347821150317391</v>
+        <v>0.2112637251083644</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8213</v>
+        <v>8086</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>814</v>
+        <v>1016.396344046898</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>37.7</v>
+        <v>140</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>76.26374717470051</v>
+        <v>76.0440152025711</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>25.9885531662656</v>
+        <v>22.915795965965</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.39680734435391</v>
+        <v>4.239634404689856</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3465120215231287</v>
+        <v>3.347821151096291</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8171</v>
+        <v>8131</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>766.0880525122293</v>
+        <v>944.6394509483092</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>21.05</v>
+        <v>68.2</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>65.9995089971093</v>
+        <v>69.22180091511886</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.28854007111986</v>
+        <v>13.43472081102026</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8969916332063047</v>
+        <v>3.366062694845725</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0707189653550136</v>
+        <v>0.736465017346602</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8070</v>
+        <v>8046</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>746.7139724510849</v>
+        <v>942.0336905180934</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>51.5</v>
+        <v>1480</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>58.25669636113798</v>
+        <v>70.77710923850941</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.83611702338915</v>
+        <v>27.21242870399245</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.466852030964424</v>
+        <v>0.7893339765290465</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1683499722360323</v>
+        <v>39.54347039347107</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8131</v>
+        <v>8150</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>744.6394509483093</v>
+        <v>929.9478003673224</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>68.2</v>
+        <v>128.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>69.2218009212973</v>
+        <v>73.68024433383519</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>13.43472079729466</v>
+        <v>39.36420958898924</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3.366062694845725</v>
+        <v>0.6448811462431668</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.7364650172687157</v>
+        <v>3.127512715736698</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8383</v>
+        <v>8081</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>728.9145586225651</v>
+        <v>882.5566699135322</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>262.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,29 +1082,29 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.37474950811176</v>
+        <v>60.42624637602845</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>18.0273405129114</v>
+        <v>14.78775873501934</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.9205436623068268</v>
+        <v>1.010177291151664</v>
       </c>
       <c r="K12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.5797516953010087</v>
+        <v>1.685251568653651</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, invest_trust_buy_2d, bb_squeeze_breakout, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>700.9646639791081</v>
+        <v>870.9646639791081</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>58</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.53565420848534</v>
+        <v>64.5356542364768</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>21.31545202516705</v>
+        <v>21.31545204250456</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>3.196466397910811</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.002797504229197</v>
+        <v>1.002797504095666</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8040</v>
+        <v>8289</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>695.2634746589586</v>
+        <v>827.1438369134291</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>90.2</v>
+        <v>55.4</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.70695334345859</v>
+        <v>70.04060178278884</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.08553532034373</v>
+        <v>30.10330203959466</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5754507913480941</v>
+        <v>2.014383691342914</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.291751824326254</v>
+        <v>1.466892014074103</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8358</v>
+        <v>8155</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>694.471218035931</v>
+        <v>802.3399327950295</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>549</v>
+        <v>334</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,49 +1241,49 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60.031029449809</v>
+        <v>52.23995102541701</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>28.17650375680101</v>
+        <v>12.96516949521539</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.386556586494211</v>
+        <v>1.048164365887169</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.562113101808308</v>
+        <v>0.289603757032211</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8155</v>
+        <v>8171</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>687.3399327950292</v>
+        <v>766.0880525122292</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>334</v>
+        <v>21.05</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.23995112986081</v>
+        <v>65.99950904318</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>12.96516959987935</v>
+        <v>21.2885400833792</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.048164365887169</v>
+        <v>0.8969916332063047</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2896037539166385</v>
+        <v>0.0707189653661435</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8431</v>
+        <v>8070</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>684.46029054505</v>
+        <v>746.7139724510816</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>64</v>
+        <v>51.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>55.91654629515885</v>
+        <v>58.25669632829599</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>32.58857049398942</v>
+        <v>17.83611693874917</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.601915864165999</v>
+        <v>1.466852030964424</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.6228415078763097</v>
+        <v>0.1683499722026474</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8150</v>
+        <v>8111</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>654.9478003673224</v>
+        <v>742.2370437796909</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>128.5</v>
+        <v>94</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>73.68024433164533</v>
+        <v>71.25729690892338</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>39.36420949466809</v>
+        <v>38.54718114057061</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6448811462431668</v>
+        <v>1.430127489951497</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>3.127512715859106</v>
+        <v>1.550604541470545</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8289</v>
+        <v>9103</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>627.1438369134291</v>
+        <v>734</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>55.4</v>
+        <v>5.35</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>70.04060178396442</v>
+        <v>69.08179933732832</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30.10330200089168</v>
+        <v>15.49846541058515</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.014383691342914</v>
+        <v>5.386011050349602</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.466892014062974</v>
+        <v>0.0332598493339511</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8147</v>
+        <v>8121</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>623.1064604096696</v>
+        <v>730.7608249906899</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>142</v>
+        <v>34.65</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>55.49649716709124</v>
+        <v>66.81328296322425</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>31.35502881830766</v>
+        <v>31.93470144798061</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.077999293039667</v>
+        <v>2.406708498968907</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.1270814126012802</v>
+        <v>0.7077184883195957</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8240</v>
+        <v>8383</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>620.8772948558201</v>
+        <v>728.9145586225651</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>55.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.92964068987634</v>
+        <v>59.37474947362372</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>38.61487697186709</v>
+        <v>18.02734053762535</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.320158779661542</v>
+        <v>0.9205436623068268</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1907229439810849</v>
+        <v>0.5797516952565001</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8215</v>
+        <v>8455</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>611.812116412363</v>
+        <v>701.0978919234402</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>27.95</v>
+        <v>23.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.21135230282785</v>
+        <v>51.98108240303533</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>38.94647897272226</v>
+        <v>9.444137079608147</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4156975415376793</v>
+        <v>1.515856040174835</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.0109171190234093</v>
+        <v>0.2552744987575215</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8110</v>
+        <v>8182</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>609.0642366840444</v>
+        <v>698.7677086827126</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>49.5</v>
+        <v>43.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.71292550423992</v>
+        <v>59.1211278095246</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>27.23932114903369</v>
+        <v>23.70005611706217</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4232510146776071</v>
+        <v>0.7011343820444057</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2656886562665217</v>
+        <v>0.5305235727573355</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8438</v>
+        <v>8040</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>595.5085472222744</v>
+        <v>695.2634746589586</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>81.7</v>
+        <v>90.2</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>67.423961927424</v>
+        <v>56.70695341448753</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.78595319007282</v>
+        <v>29.08553533862792</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7279311692160035</v>
+        <v>0.5754507913480941</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.950564655365878</v>
+        <v>0.2917518240592027</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>9103</v>
+        <v>8358</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>594</v>
+        <v>694.471218035931</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>5.35</v>
+        <v>549</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>69.08179935570058</v>
+        <v>60.031029449809</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15.49846530559192</v>
+        <v>28.17650375680101</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>5.386011050349602</v>
+        <v>1.386556586494211</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.0332598493317255</v>
+        <v>3.562113101808308</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8455</v>
+        <v>8438</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>586.097891923447</v>
+        <v>690.5085472222744</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>23.2</v>
+        <v>81.7</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.98108240645498</v>
+        <v>67.42396191885322</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>9.444137106432516</v>
+        <v>31.78595319007282</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.515856040174835</v>
+        <v>0.7279311692160035</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.2552744987018873</v>
+        <v>0.950564655443772</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8182</v>
+        <v>8431</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>583.7677086827126</v>
+        <v>684.46029054505</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>43.8</v>
+        <v>64</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.12112781873641</v>
+        <v>55.91654625384844</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.70005609453769</v>
+        <v>32.58857054298011</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7011343820444057</v>
+        <v>0.601915864165999</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.5305235727684674</v>
+        <v>-0.6228415078095493</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8064</v>
+        <v>9110</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>581.1554946843809</v>
+        <v>679</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>136</v>
+        <v>3.38</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>57.76730312358805</v>
+        <v>54.25538671334344</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.75544990353358</v>
+        <v>5.167028604476926</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.2977573832787852</v>
+        <v>6.436700898212353</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.3416380095800058</v>
+        <v>0.0983669815252497</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8089</v>
+        <v>8091</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>569.4800295505853</v>
+        <v>645.8788992886285</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>19.35</v>
+        <v>233.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>58.36454233377057</v>
+        <v>61.31090135587172</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>28.68865640287074</v>
+        <v>20.16603146760933</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4126782507511267</v>
+        <v>1.033382387551004</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0565080252600318</v>
+        <v>3.108695058629574</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8046</v>
+        <v>8085</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>567.0336905180934</v>
+        <v>641.8112031605629</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1480</v>
+        <v>15.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>70.77710923850941</v>
+        <v>64.16993953618621</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>27.21242872596435</v>
+        <v>19.05167485172742</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7893339765290465</v>
+        <v>0.971899522413924</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>39.54347039380495</v>
+        <v>-0.0142366521475163</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8081</v>
+        <v>8110</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>562.5566699135323</v>
+        <v>639.0642366840444</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>262.5</v>
+        <v>49.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>60.42624652594868</v>
+        <v>58.71292550635386</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>14.78775844578562</v>
+        <v>27.23932108484281</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.010177291151664</v>
+        <v>0.4232510146776071</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.685251566650784</v>
+        <v>0.2656886562776483</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8121</v>
+        <v>8215</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>560.7608249906913</v>
+        <v>631.812116412363</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>34.65</v>
+        <v>27.95</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>66.81328300775982</v>
+        <v>54.21135227469164</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.93470143663567</v>
+        <v>38.94647904466048</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.406708498968907</v>
+        <v>0.4156975415376793</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>2</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.7077184881193057</v>
+        <v>0.0109171190790448</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8940</v>
+        <v>8147</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>555.0896798412631</v>
+        <v>623.1064604096689</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>15.15</v>
+        <v>142</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.51978120612657</v>
+        <v>55.49649715995965</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>10.25972141576399</v>
+        <v>31.35502885885735</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.212991441260026</v>
+        <v>1.077999293039667</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.0453408539566909</v>
+        <v>0.1270814129350732</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8045</v>
+        <v>8240</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>553.8048592281102</v>
+        <v>620.8772948558202</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>55.9</v>
+        <v>55.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>58.72816000244558</v>
+        <v>58.92964085196628</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.53402398529231</v>
+        <v>38.61487696701407</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4502455379513297</v>
+        <v>0.320158779661542</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.3931402880766679</v>
+        <v>0.190722943836433</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8111</v>
+        <v>8467</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>542.2370437796909</v>
+        <v>587.5226239575958</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>94</v>
+        <v>91.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>71.25729702432331</v>
+        <v>53.71438640139322</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>38.54718110542616</v>
+        <v>7.597228952508068</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.430127489951497</v>
+        <v>1.000479856637521</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.550604540335586</v>
+        <v>0.7737856267534959</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8054</v>
+        <v>8162</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>539.7084276232302</v>
+        <v>584.6576285856275</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>81.3</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>41.16408769454497</v>
+        <v>55.76291022834849</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.15407701032709</v>
+        <v>22.12260118844048</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.873732133934528</v>
+        <v>0.5269105015268487</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0019482521733877</v>
+        <v>0.3334989164999278</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8085</v>
+        <v>8064</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>526.8112031605629</v>
+        <v>581.155494684381</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>15.1</v>
+        <v>136</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>64.16993964726825</v>
+        <v>57.76730311752971</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.05167477485719</v>
+        <v>23.75544977975897</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.971899522413924</v>
+        <v>0.2977573832787852</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0142366522699164</v>
+        <v>-0.3416380093351936</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8050</v>
+        <v>8089</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>524.0795410348265</v>
+        <v>569.4800295505851</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>60.6</v>
+        <v>19.35</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>53.16629536490937</v>
+        <v>58.36454274281592</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>27.13617057019721</v>
+        <v>28.68865640881418</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.6481818413439754</v>
+        <v>0.4126782507511267</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1371845567709779</v>
+        <v>0.0565080254046823</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8277</v>
+        <v>8039</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>512.1557943502701</v>
+        <v>565.2566401661383</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>15.5</v>
+        <v>304.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,49 +2513,49 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>79.39988699592664</v>
+        <v>58.161626062035</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>37.00445211105061</v>
+        <v>18.88639441501162</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3205821000936222</v>
+        <v>0.8561000932618478</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.2251672638038413</v>
+        <v>2.321946735775724</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>9110</v>
+        <v>8261</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>509</v>
+        <v>563.2554287507786</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>3.38</v>
+        <v>191</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>54.25538671239146</v>
+        <v>55.22766986631954</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5.167028604953334</v>
+        <v>17.30578865174321</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>6.436700898212353</v>
+        <v>1.53861905171978</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.098366981531926</v>
+        <v>3.554878981186063</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8091</v>
+        <v>8093</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>505.8788992886306</v>
+        <v>557.778656484036</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>233.5</v>
+        <v>26.35</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>61.3109013723889</v>
+        <v>54.3260992371638</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.16603150891295</v>
+        <v>12.73365245818254</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.033382387551004</v>
+        <v>1.258897155229692</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>3.10869505829578</v>
+        <v>0.2040890623793185</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8299</v>
+        <v>8940</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>503.6894653966978</v>
+        <v>555.089679841263</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2060</v>
+        <v>15.15</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,49 +2672,49 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>47.78381093387826</v>
+        <v>53.51978103706713</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>13.27674221186924</v>
+        <v>10.25972144083469</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5365150412263741</v>
+        <v>2.212991441260026</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-4.685172392113316</v>
+        <v>0.0453408539678196</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8109</v>
+        <v>8045</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>達運光電</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>503.2208275196909</v>
+        <v>553.8048592281098</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>135</v>
+        <v>55.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.8726049585995</v>
+        <v>58.72816035600767</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.90783668560358</v>
+        <v>22.53402410941081</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.359912091663644</v>
+        <v>0.4502455379513297</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.4878696895052594</v>
+        <v>0.3931402886330213</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8162</v>
+        <v>8464</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>489.6576285856277</v>
+        <v>544.3941927179753</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>365.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>55.76291022351806</v>
+        <v>45.95294856615386</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>22.12260117786051</v>
+        <v>10.81661312846978</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5269105015268487</v>
+        <v>0.8016686220831704</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.3334989165110522</v>
+        <v>-1.003062629904252</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, invest_trust_buy_2d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8112</v>
+        <v>8054</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>486.123852030115</v>
+        <v>539.7084276232307</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>83.7</v>
+        <v>81.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>41.83710249446965</v>
+        <v>41.16408760209035</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.08222704062193</v>
+        <v>23.15407704148637</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5522715296876817</v>
+        <v>1.873732133934528</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.2939252799890619</v>
+        <v>-0.0019482520621151</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8096</v>
+        <v>8050</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>466.213225425035</v>
+        <v>524.0795410348265</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>41.41615966155626</v>
+        <v>53.16629533721459</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>32.43180977562357</v>
+        <v>27.13617052398592</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4144938495884113</v>
+        <v>0.6481818413439754</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.476335977567128</v>
+        <v>0.1371845568154845</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8488</v>
+        <v>8277</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>455.0090059123195</v>
+        <v>512.1557943502705</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>9.82</v>
+        <v>15.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>47.54843931825835</v>
+        <v>79.39988700150222</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>35.94213790346942</v>
+        <v>37.00445200848635</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4264205777409219</v>
+        <v>0.3205821000936222</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0252308229318319</v>
+        <v>0.2251672638190966</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8048</v>
+        <v>8299</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>453.8422979433933</v>
+        <v>503.6894653966977</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>51.5</v>
+        <v>2060</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>55.2757317353365</v>
+        <v>47.78381084363092</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>13.13792976448291</v>
+        <v>13.2767422196509</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>2.235454650283796</v>
+        <v>0.5365150412263741</v>
       </c>
       <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.3867105628855503</v>
+        <v>-4.685172389665418</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8103</v>
+        <v>8109</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>451.9314666230262</v>
+        <v>503.220827519691</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.73928276159134</v>
+        <v>51.87260497367567</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>35.73383463329868</v>
+        <v>28.90783664524884</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5004624386729418</v>
+        <v>1.359912091663644</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-1.610348074748658</v>
+        <v>0.4878696896165555</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8039</v>
+        <v>8112</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>435.2566401661382</v>
+        <v>501.1238520301149</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>304.5</v>
+        <v>83.7</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>58.16162606011608</v>
+        <v>41.83710245083832</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.88639445919495</v>
+        <v>20.08222704835116</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8561000932618478</v>
+        <v>0.5522715296876817</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>2.321946735708961</v>
+        <v>0.2939252801670935</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>9912</v>
+        <v>8103</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>430.1441509824824</v>
+        <v>466.9314666230262</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>13.05</v>
+        <v>118</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.73095326253295</v>
+        <v>51.73928279911662</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>33.76069363999015</v>
+        <v>35.73383481522023</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.5210555183131208</v>
+        <v>0.5004624386729418</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.0036862980630899</v>
+        <v>-1.610348075397042</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8068</v>
+        <v>8096</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>429.7241359456144</v>
+        <v>466.2132254250351</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>17.05</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.22121416324547</v>
+        <v>41.4161596639424</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>28.16198813677876</v>
+        <v>32.43180984331513</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.556069438089714</v>
+        <v>0.4144938495884113</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0563702357214305</v>
+        <v>1.476335977511496</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8473</v>
+        <v>8488</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>425.7437825058416</v>
+        <v>455.0090059123195</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>40.1</v>
+        <v>9.82</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.57556818953193</v>
+        <v>47.54843937479048</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>22.80881249035023</v>
+        <v>35.94213774157564</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3938345615512624</v>
+        <v>0.4264205777409219</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.322805605927724</v>
+        <v>-0.0252308229318319</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8261</v>
+        <v>8463</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>423.2554287507788</v>
+        <v>454.8756444337899</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>191</v>
+        <v>21.25</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.2276699027837</v>
+        <v>50.97445756490119</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.30578863290302</v>
+        <v>25.95374989446054</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.53861905171978</v>
+        <v>0.2222392079058756</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>3.55487898045165</v>
+        <v>0.0070194051248298</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8443</v>
+        <v>8048</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>422.7606981240039</v>
+        <v>453.8422979433933</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11.15</v>
+        <v>51.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>44.61126931937078</v>
+        <v>55.2757315487404</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>52.1945475713517</v>
+        <v>13.13792974720494</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.1198669414627263</v>
+        <v>2.235454650283796</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.001404537713568</v>
+        <v>0.3867105632638669</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8072</v>
+        <v>9912</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>420.9682173520404</v>
+        <v>430.1441509824824</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.9</v>
+        <v>13.05</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.05622863315737</v>
+        <v>52.73095336021117</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>37.83518907128762</v>
+        <v>33.76069360734315</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3468905491116208</v>
+        <v>0.5210555183131208</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0265780521567107</v>
+        <v>-0.0036862980853444</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8059</v>
+        <v>8068</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>414.609357889374</v>
+        <v>429.7241359456145</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>17.55</v>
+        <v>17.05</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>59.97713281434662</v>
+        <v>48.22121430866667</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>27.09127427816289</v>
+        <v>28.16198809698476</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2807665701187863</v>
+        <v>0.556069438089714</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>2</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1765747662321725</v>
+        <v>0.0563702358438289</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8102</v>
+        <v>8473</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>412.9382392242341</v>
+        <v>425.7437825058424</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>60.8</v>
+        <v>40.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.19971580823298</v>
+        <v>46.57556822763821</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>5.461488268423248</v>
+        <v>22.80881244757872</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2.119483932976016</v>
+        <v>0.3938345615512624</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>1.185369442153525</v>
+        <v>0.3228056059054733</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8466</v>
+        <v>8104</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>400.9059474402318</v>
+        <v>424.2169166787656</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>15.35</v>
+        <v>30.95</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.94329363812622</v>
+        <v>48.5751410617034</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>27.37861688754754</v>
+        <v>17.08424770345788</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.3038401894092996</v>
+        <v>0.5520184677128928</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,48 +3591,48 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0971194498019264</v>
+        <v>0.1254053281228296</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8183</v>
+        <v>8443</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>395.8634049635201</v>
+        <v>422.7606981240039</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>28.2</v>
+        <v>11.15</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G60" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>44.90268849549037</v>
+        <v>44.61126946743668</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.145376275842</v>
+        <v>52.19454757135171</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.870816255095116</v>
+        <v>0.1198669414627263</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0686206106093753</v>
+        <v>0.001404537713568</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8423</v>
+        <v>8072</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>391.5552289921668</v>
+        <v>420.9682173520403</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>17.95</v>
+        <v>26.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>49.73948984161536</v>
+        <v>48.05622872967945</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.69655292795347</v>
+        <v>37.83518912012465</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.149257610070035</v>
+        <v>0.3468905491116208</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0151304809462644</v>
+        <v>-0.0265780523792527</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8097</v>
+        <v>8059</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>391.3928175726234</v>
+        <v>414.609357889374</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>48.3</v>
+        <v>17.55</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>39.80010110696223</v>
+        <v>59.97713217925101</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>18.95005576704716</v>
+        <v>27.09127410513373</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.08385928013157069</v>
+        <v>0.2807665701187863</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.08663764028680621</v>
+        <v>0.1765747662893836</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8038</v>
+        <v>8102</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>390.5044209777894</v>
+        <v>412.9382392242341</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>34.1</v>
+        <v>60.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>57.01709388211724</v>
+        <v>51.19971580136488</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>30.49606270563474</v>
+        <v>5.461488268423247</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.7420501686285069</v>
+        <v>2.119483932976016</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.323980770191077</v>
+        <v>1.185369442576349</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8093</v>
+        <v>8466</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>387.7786564840359</v>
+        <v>400.9059474402318</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>26.35</v>
+        <v>15.35</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.32609919605815</v>
+        <v>51.94329362585672</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12.73365239313492</v>
+        <v>27.37861684586981</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.258897155229692</v>
+        <v>0.3038401894092996</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,51 +3856,51 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.2040890624746688</v>
+        <v>0.0971194498019264</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8047</v>
+        <v>8183</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>382.9748695494474</v>
+        <v>395.8634049635208</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>46.95</v>
+        <v>28.2</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G65" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.43354709086475</v>
+        <v>44.9026885539789</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>9.454371033673889</v>
+        <v>19.14537614643788</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.9446006874693094</v>
+        <v>1.870816255095116</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.179285839354658</v>
+        <v>0.0686206106538616</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8163</v>
+        <v>8423</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>379.1645703314005</v>
+        <v>391.5552289921668</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>29.9</v>
+        <v>17.95</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.31622573984603</v>
+        <v>49.73948981540314</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12.78349068010739</v>
+        <v>19.69655291011314</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.82260228102676</v>
+        <v>1.149257610070035</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1150058982506574</v>
+        <v>-0.0151304809240096</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8069</v>
+        <v>8097</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>376.2698932874109</v>
+        <v>391.3928175726234</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>145</v>
+        <v>48.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>41.72327977665569</v>
+        <v>39.8001011914083</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>28.41826874187898</v>
+        <v>18.95005576854647</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.113544336112381</v>
+        <v>0.08385928013157069</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.263524249571388</v>
+        <v>0.0866376401310282</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8071</v>
+        <v>8038</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>371.4218668892119</v>
+        <v>390.5044209777895</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>21.9</v>
+        <v>34.1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>44.3345356142782</v>
+        <v>57.01709414753233</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10.26763277189521</v>
+        <v>30.49606274333667</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.6791028935994171</v>
+        <v>0.7420501686285069</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>1</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.08774129894917899</v>
+        <v>0.3239807697682432</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8467</v>
+        <v>8047</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>362.5226239575956</v>
+        <v>382.9748695494471</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>91.5</v>
+        <v>46.95</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.7143866194016</v>
+        <v>51.43354708908935</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7.597228921252826</v>
+        <v>9.454371059034784</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.000479856637521</v>
+        <v>0.9446006874693094</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.773785626085858</v>
+        <v>1.179285839354658</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8087</v>
+        <v>8163</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>349.1603141978349</v>
+        <v>379.1645703314005</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>23.5</v>
+        <v>29.9</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.61235516113194</v>
+        <v>43.31622567610819</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>5.170933001229388</v>
+        <v>12.78349066438337</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.0813652422203939</v>
+        <v>1.82260228102676</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.1273408272881226</v>
+        <v>0.1150058983174207</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8463</v>
+        <v>8069</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>344.8756444337899</v>
+        <v>376.269893287411</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>21.25</v>
+        <v>145</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.97445807568921</v>
+        <v>41.72327964235257</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>25.95374926347642</v>
+        <v>28.41826877406866</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.2222392079058756</v>
+        <v>1.113544336112381</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0070194046129853</v>
+        <v>1.263524249015042</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8049</v>
+        <v>8071</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>334.3356207069989</v>
+        <v>371.4218668892119</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>24.65</v>
+        <v>21.9</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>49.64987816571365</v>
+        <v>44.33453568636307</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14.85780096179109</v>
+        <v>10.26763271448591</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6324909685991671</v>
+        <v>0.6791028935994171</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0512591578440579</v>
+        <v>0.08774129890467131</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8477</v>
+        <v>8210</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>333.1874011472142</v>
+        <v>366.1336557991847</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>14.1</v>
+        <v>872</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>36.57169047015133</v>
+        <v>41.81273483489011</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>25.51948196010971</v>
+        <v>19.7444465468995</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.9525006440910148</v>
+        <v>1.456163127840641</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0503826620006143</v>
+        <v>5.031507968224446</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8440</v>
+        <v>8087</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>330.9652142943413</v>
+        <v>349.1603141978349</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>20.15</v>
+        <v>23.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.52997953229804</v>
+        <v>49.61235517280489</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.1473023746614</v>
+        <v>5.170932918130051</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.284471847539146</v>
+        <v>0.0813652422203939</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0012555106161554</v>
+        <v>0.1273408272213569</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>9930</v>
+        <v>8105</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>323.4498944446441</v>
+        <v>340.3671544746965</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>58.7</v>
+        <v>15.15</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>17.63446994300477</v>
+        <v>47.75107640080824</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>33.93394834174914</v>
+        <v>20.57725078990914</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.94871002864887</v>
+        <v>0.4777100254623995</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1600682667742829</v>
+        <v>0.1081431384995354</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8410</v>
+        <v>8049</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>320.6730178565263</v>
+        <v>334.3356207069989</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>26.7</v>
+        <v>24.65</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>21.30445821451272</v>
+        <v>49.64987816571365</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>47.42925252807751</v>
+        <v>14.85780100611569</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.357243880326383</v>
+        <v>0.6324909685991671</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1126454536454527</v>
+        <v>0.05125915783293</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8105</v>
+        <v>8477</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>320.3671544746965</v>
+        <v>333.1874011472142</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>15.15</v>
+        <v>14.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>47.751076447347</v>
+        <v>36.57169057606572</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20.57725074958353</v>
+        <v>25.5194819419434</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4777100254623995</v>
+        <v>0.9525006440910148</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1081431384465635</v>
+        <v>-0.0503826620228682</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8176</v>
+        <v>8440</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>317.0652874012237</v>
+        <v>330.9652142943415</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>9.720000000000001</v>
+        <v>20.15</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>41.86932972858493</v>
+        <v>49.52997954834963</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>25.76946710117352</v>
+        <v>18.14730237866548</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.69524043718362</v>
+        <v>1.284471847539146</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0023805119298098</v>
+        <v>-0.0012555105827748</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8104</v>
+        <v>9930</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>314.2169166787671</v>
+        <v>323.4498944446451</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>30.95</v>
+        <v>58.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>48.5751409826827</v>
+        <v>17.63446994300477</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.08424764849651</v>
+        <v>33.93394833926046</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5520184677128928</v>
+        <v>0.94871002864887</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.1254053281450833</v>
+        <v>-0.1600682667520252</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8499</v>
+        <v>8410</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>311.8373066446693</v>
+        <v>320.6730178565269</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>252.5</v>
+        <v>26.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.62757435924786</v>
+        <v>21.3044586466314</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>8.726748040680684</v>
+        <v>47.42925254176024</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7256658333032062</v>
+        <v>1.357243880326383</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>2.905633590302444</v>
+        <v>-0.1126454535898184</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8482</v>
+        <v>8176</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>308.1412385577996</v>
+        <v>317.0652874012237</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>48</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>49.87580416070295</v>
+        <v>41.86933127241035</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4.109847870925837</v>
+        <v>25.76946706210878</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.7714109673444239</v>
+        <v>1.69524043718362</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0408770919087445</v>
+        <v>-0.0023805119409361</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8411</v>
+        <v>8499</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>300.4005261368029</v>
+        <v>311.8373066446694</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>11.7</v>
+        <v>252.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>25.95829342790196</v>
+        <v>50.62757436925858</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>34.63157370084397</v>
+        <v>8.726747998524329</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5108093875089703</v>
+        <v>0.7256658333032062</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0740230705866174</v>
+        <v>2.905633590747524</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8442</v>
+        <v>8482</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>299.9738221396313</v>
+        <v>308.1412385577996</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>46.1</v>
+        <v>48</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>54.44532535107582</v>
+        <v>49.87580142571066</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>10.44223124082719</v>
+        <v>4.109847871396299</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.936223188877244</v>
+        <v>0.7714109673444239</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0015960880202257</v>
+        <v>0.0408770919087445</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8114</v>
+        <v>8411</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>298.7461783738349</v>
+        <v>300.4005261368029</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>177.5</v>
+        <v>11.7</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.32970024665442</v>
+        <v>25.958293500764</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>24.31240872611881</v>
+        <v>34.63157370084397</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9681318176505443</v>
+        <v>0.5108093875089703</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.056405505894007</v>
+        <v>-0.0740230706088732</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8088</v>
+        <v>8442</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>293.0484400037541</v>
+        <v>299.9738221396313</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>44.45</v>
+        <v>46.1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>53.57653436518341</v>
+        <v>54.44532511806725</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.16737486741058</v>
+        <v>10.44223136212199</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9440336535811028</v>
+        <v>0.936223188877244</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>1</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.4317598890858488</v>
+        <v>-0.0015960877086538</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8462</v>
+        <v>8114</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>287.9268430429112</v>
+        <v>298.7461783738349</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>158</v>
+        <v>177.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>41.32124856081217</v>
+        <v>39.32970007741113</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>31.01292117094872</v>
+        <v>24.31240889163084</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4185847113972268</v>
+        <v>0.9681318176505443</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.0551987894625023</v>
+        <v>1.056405508119442</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8932</v>
+        <v>8088</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>281.6277561657166</v>
+        <v>293.0484400037541</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>44.45</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>41.55337430981122</v>
+        <v>53.57653438309158</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>17.66897822689904</v>
+        <v>13.1673748705636</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3075229236037267</v>
+        <v>0.9440336535811028</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>1</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2890601228262626</v>
+        <v>0.4317598890524611</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8367</v>
+        <v>8462</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>280.5052206797924</v>
+        <v>287.9268430429112</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>40.9</v>
+        <v>158</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>53.92689331587003</v>
+        <v>41.32124860964923</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.94886562671704</v>
+        <v>31.01292119662783</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2081197536478768</v>
+        <v>0.4185847113972268</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0396802771819584</v>
+        <v>-0.0551987897963335</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>9955</v>
+        <v>8932</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>277.1683299684933</v>
+        <v>281.6277561657166</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>23.9</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>54.40000242052173</v>
+        <v>41.55337408516767</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>13.47988324240811</v>
+        <v>17.66897810584986</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.537004105103957</v>
+        <v>0.3075229236037267</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.1106846597999399</v>
+        <v>0.2890601239704642</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8464</v>
+        <v>8367</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>264.3941927179753</v>
+        <v>280.5052206797924</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>365.5</v>
+        <v>40.9</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>45.952949476307</v>
+        <v>53.92689326593881</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>10.81661270306842</v>
+        <v>14.9488657269354</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8016686220831704</v>
+        <v>0.2081197536478768</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-1.003062636914383</v>
+        <v>0.0396802771597007</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8271</v>
+        <v>9955</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>262.9590970406488</v>
+        <v>277.1683299684906</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>202</v>
+        <v>23.9</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>41.9880055055817</v>
+        <v>54.40000239986244</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.94888379090924</v>
+        <v>13.47988328112646</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.9352049805612532</v>
+        <v>1.537004105103957</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.322780753747776</v>
+        <v>0.1106846598110665</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8234</v>
+        <v>8271</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>261.3402601877667</v>
+        <v>262.959097040649</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>61.8</v>
+        <v>202</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>41.30006627545148</v>
+        <v>41.98800549868822</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>18.69771536176097</v>
+        <v>12.94888384577119</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7534666738818385</v>
+        <v>0.9352049805612532</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1462964722710265</v>
+        <v>0.3227807536810188</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8210</v>
+        <v>8234</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>251.1336557991848</v>
+        <v>261.3402601877666</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>872</v>
+        <v>61.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>41.81273483489011</v>
+        <v>41.30006636464768</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.74444651587119</v>
+        <v>18.69771567482499</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.456163127840641</v>
+        <v>0.7534666738818385</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>5.031507967779326</v>
+        <v>0.146296471937223</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8076</v>
+        <v>8454</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>243.2198204233088</v>
+        <v>253.020428430145</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>21.35</v>
+        <v>244.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>39.86301731397831</v>
+        <v>50.69099645033335</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.66648000925309</v>
+        <v>12.0482408795681</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9300376329823112</v>
+        <v>0.8456609941746599</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0547595489760012</v>
+        <v>0.5742375801377464</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8044</v>
+        <v>8076</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>240.5700360105997</v>
+        <v>243.2198204233096</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.1</v>
+        <v>21.35</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.80351218855616</v>
+        <v>39.86301719815855</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.70408474579122</v>
+        <v>21.66648000925309</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5439435747927877</v>
+        <v>0.9300376329823112</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>1</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1027942845885162</v>
+        <v>0.0547595490538901</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8374</v>
+        <v>8044</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>239.2789092397978</v>
+        <v>240.5700360105997</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>75.59999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>40.79450823087536</v>
+        <v>48.80351205776404</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>9.26470900981375</v>
+        <v>16.70408474579121</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8042702132524877</v>
+        <v>0.5439435747927877</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0469698566576228</v>
+        <v>0.1027942846330218</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8454</v>
+        <v>8374</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>233.020428430145</v>
+        <v>239.2789092397977</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>244.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.69099651885248</v>
+        <v>40.7945087459872</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.04824078572824</v>
+        <v>9.26470898918711</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8456609941746599</v>
+        <v>0.8042702132524877</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,11 +5605,11 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.5742375796926793</v>
+        <v>0.0469698561012692</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.83534425630317</v>
+        <v>41.8353442792915</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.97965403605323</v>
+        <v>11.97965408730603</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.6576192169412509</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.0114626685618616</v>
+        <v>0.0114626684505905</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>222.8489399905349</v>
+        <v>222.848939990535</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>91.8</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>46.09105424251291</v>
+        <v>46.09105418244544</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.60455074476621</v>
+        <v>20.60455074964792</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>1.058807731311683</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.2789770337229813</v>
+        <v>0.2789770339232682</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5721,21 +5721,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8472</v>
+        <v>8404</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>218.8234371498992</v>
+        <v>221.9316946555556</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>40.68235585379223</v>
+        <v>36.43761676969329</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>28.16013631768202</v>
+        <v>49.9411684073793</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.08234371498991699</v>
+        <v>0.342850467961608</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.341167333936981</v>
+        <v>0.0508886999640205</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5774,21 +5774,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8080</v>
+        <v>8472</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>216.6594813872869</v>
+        <v>218.8234371498992</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>28.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.6948280566592</v>
+        <v>40.68235614132101</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>34.45953446239638</v>
+        <v>28.16013628828141</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.424331158511849</v>
+        <v>0.08234371498991699</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.1631143844366088</v>
+        <v>-1.341167333981481</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8404</v>
+        <v>8080</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>201.9316946555555</v>
+        <v>216.6594813872869</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>13.5</v>
+        <v>28.3</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>36.43761660015434</v>
+        <v>51.69482805583181</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>49.94116830539632</v>
+        <v>34.45953446107274</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.342850467961608</v>
+        <v>2.424331158511849</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0508886999306389</v>
+        <v>-0.1631143844366088</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8249</v>
+        <v>8422</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>188.533318755986</v>
+        <v>206.0202511071636</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>39.7</v>
+        <v>25.6</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>48.91478095933377</v>
+        <v>44.81020709558601</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>16.61808926358387</v>
+        <v>8.586934628016001</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6287659015918201</v>
+        <v>0.940847306621724</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.2395327861629042</v>
+        <v>-0.0304603768808762</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8422</v>
+        <v>8478</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>186.0202511071636</v>
+        <v>196.4859882022829</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>25.6</v>
+        <v>139.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>44.81020818239308</v>
+        <v>42.19054745638596</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>8.586934611586461</v>
+        <v>7.320805184984737</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.940847306621724</v>
+        <v>0.8776739266518445</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0304603770715768</v>
+        <v>0.1185211511863304</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8092</v>
+        <v>8249</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>174.9789968913274</v>
+        <v>188.5333187559861</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>12</v>
+        <v>39.7</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>29.51593555724064</v>
+        <v>48.91478065337619</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>12.68258806612885</v>
+        <v>16.6180895212316</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.950860227872363</v>
+        <v>0.6287659015918201</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.0626465194866784</v>
+        <v>0.2395327866079931</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8101</v>
+        <v>8092</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>166.5836362554693</v>
+        <v>174.9789968913277</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.52186979301312</v>
+        <v>29.5159354513824</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.14661935372631</v>
+        <v>12.68258806612885</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5298771665178709</v>
+        <v>1.950860227872363</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1206189581343822</v>
+        <v>-0.0626465194978037</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8341</v>
+        <v>8101</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>163.5714955520767</v>
+        <v>166.5836362554693</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>73.59999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>33.08437950911546</v>
+        <v>41.52186987028418</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.26383427140171</v>
+        <v>15.14661937735304</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.104914784283393</v>
+        <v>0.5298771665178709</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0410616261964558</v>
+        <v>-0.1206189581900175</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8481</v>
+        <v>8341</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>161.1461859674915</v>
+        <v>163.5714955520767</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>40.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.32032753759062</v>
+        <v>33.08437950911546</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.3738726075671</v>
+        <v>13.26383427953172</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.388837450464798</v>
+        <v>1.104914784283393</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0570292944942604</v>
+        <v>-0.0410616262632242</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8222</v>
+        <v>8481</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>157.5297611335683</v>
+        <v>161.1461859674912</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>35.05</v>
+        <v>40.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>40.12550042511798</v>
+        <v>42.32032801995872</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>9.458398204136175</v>
+        <v>11.37387284805855</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.92524047159056</v>
+        <v>1.388837450464798</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.113006925449127</v>
+        <v>-0.0570292946722953</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8291</v>
+        <v>8222</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>156.7252724307105</v>
+        <v>157.5297611335683</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>27.7</v>
+        <v>35.05</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.69511174053554</v>
+        <v>40.12550048611914</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>5.426931803559261</v>
+        <v>9.458398211178087</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9192120759521564</v>
+        <v>0.92524047159056</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,11 +6294,11 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0664572144724928</v>
+        <v>0.1130069252043294</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>35.09841980649031</v>
+        <v>35.09841990204774</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.63165373702937</v>
+        <v>17.63165384961262</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.2174252157034145</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.063327716879993</v>
+        <v>0.0633277168733168</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>133.4490225915927</v>
+        <v>133.4490225915933</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>5.89</v>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>41.42830944010458</v>
+        <v>41.42830882159167</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>7.740660392523274</v>
+        <v>7.740660497348434</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.3996248852879407</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.004894343899689</v>
+        <v>0.0048943439352956</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>37.53829748739608</v>
+        <v>37.53829750033195</v>
       </c>
       <c r="I113" s="2" t="n">
         <v>17.42984472736538</v>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8478</v>
+        <v>8291</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>86.48598820228307</v>
+        <v>96.72527243071048</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>139.5</v>
+        <v>27.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.19054749046305</v>
+        <v>37.67829879954562</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7.320805184984738</v>
+        <v>5.429655453900715</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8776739266518445</v>
+        <v>0.9192120759521564</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1185211508525219</v>
+        <v>0.0665184266063838</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
